--- a/docs/downloads/经营分_鲁东省区__青岛前海片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁东省区__青岛前海片区_2026-10-18.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>7274834328603854885</t>
+          <t>7376243478881945636</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>锦江之星品尚（青岛栈桥火车站酒店）</t>
+          <t>维也纳酒店（5.0奥帆中心北青岛大学店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>锦江之星品尚青岛栈桥河南路店</t>
+          <t>青岛维也纳酒店(5.0青岛大学奥帆中心北店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1061,7 +1061,7 @@
         <v>87</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>6725661947091601416</t>
+          <t>7274834328603854885</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>喆啡酒店（青岛北站李村步行街地铁站店）</t>
+          <t>锦江之星品尚（青岛栈桥火车站酒店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>喆啡酒店(青岛北站李村步行街地铁站店)</t>
+          <t>锦江之星品尚青岛栈桥河南路店</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
         <v>30</v>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7232891566909327397</t>
+          <t>6725661947091601416</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（青岛香港中路奥帆中心小麦岛公园店）</t>
+          <t>喆啡酒店（青岛北站李村步行街地铁站店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>白玉兰(商务)酒店(青岛奥帆中心小麦岛公园店)</t>
+          <t>喆啡酒店(青岛北站李村步行街地铁站店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7376243478881945636</t>
+          <t>7232891566909327397</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0奥帆中心北青岛大学店）</t>
+          <t>白玉兰商务酒店（青岛香港中路奥帆中心小麦岛公园店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>青岛维也纳酒店(5.0青岛大学奥帆中心北店)</t>
+          <t>白玉兰(商务)酒店(青岛奥帆中心小麦岛公园店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2557,7 +2557,7 @@
         <v>110</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>110</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>120</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H27" t="n">
